--- a/From.xlsx
+++ b/From.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C918FE-DF2C-4810-BB42-1B97C0EB299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07D897E-BD82-4BEC-8B58-2885B63AE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Question</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t xml:space="preserve">	Are you okay with the class timings as attendance percentage set by Anudip parameters to be able to get placement benefits? </t>
-  </si>
-  <si>
-    <t>Test Question(For Only Test)</t>
   </si>
 </sst>
 </file>
@@ -378,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="108.26953125" bestFit="1" customWidth="1"/>
@@ -439,11 +436,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/From.xlsx
+++ b/From.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07D897E-BD82-4BEC-8B58-2885B63AE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A300A780-5F1A-4F04-A60C-3D4F4A0867E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Question</t>
   </si>
@@ -48,16 +48,13 @@
     <t>Willing to relocate or not?</t>
   </si>
   <si>
-    <t xml:space="preserve">	As most of the job locations are bit far away from your current location therefore are you okay with the distance? </t>
-  </si>
-  <si>
     <t xml:space="preserve">	Are you willing to do rotational shift?</t>
   </si>
   <si>
     <t xml:space="preserve">	What is your expected Salary as a fresher?</t>
   </si>
   <si>
-    <t xml:space="preserve">	Are you okay with the class timings as attendance percentage set by Anudip parameters to be able to get placement benefits? </t>
+    <t xml:space="preserve">	Are you okay with the class timings ? </t>
   </si>
 </sst>
 </file>
@@ -375,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="108.26953125" bestFit="1" customWidth="1"/>
@@ -431,11 +428,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/From.xlsx
+++ b/From.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A300A780-5F1A-4F04-A60C-3D4F4A0867E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF700A-2449-4B75-9806-B516A321EB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,13 +48,13 @@
     <t>Willing to relocate or not?</t>
   </si>
   <si>
-    <t xml:space="preserve">	Are you willing to do rotational shift?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	What is your expected Salary as a fresher?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Are you okay with the class timings ? </t>
+    <t>Are you willing to do rotational shift?</t>
+  </si>
+  <si>
+    <t>What is your expected Salary as a fresher?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you okay with the class timings ? </t>
   </si>
 </sst>
 </file>
